--- a/artfynd/A 48952-2023 artfynd.xlsx
+++ b/artfynd/A 48952-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48952-2023 artfynd.xlsx
+++ b/artfynd/A 48952-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105310631</v>
+        <v>105310629</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599136.2023148867</v>
+        <v>599066</v>
       </c>
       <c r="R2" t="n">
-        <v>6564516.460853742</v>
+        <v>6564631</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,21 +743,11 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På Stig.</t>
+          <t>Ca 2 dm2.</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105315441</v>
+        <v>105310630</v>
       </c>
       <c r="B3" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tåsjön, Srm</t>
+          <t>Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599307.1225231502</v>
+        <v>599077</v>
       </c>
       <c r="R3" t="n">
-        <v>6564515.791946011</v>
+        <v>6564554</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,21 +850,11 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,6 +863,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stor blåmossa i barrblandskog.</t>
+        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -914,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105315439</v>
+        <v>105310631</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dammkärr, Srm</t>
+          <t>Tåsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599072.2463475044</v>
+        <v>599136</v>
       </c>
       <c r="R4" t="n">
-        <v>6564528.628602174</v>
+        <v>6564516</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,21 +957,11 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +973,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Två fruktkroppar på gammal tall norr om kolbotten.</t>
+          <t>På Stig.</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1039,16 +999,11 @@
         <v>105315437</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1076,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599025.1687030385</v>
+        <v>599025</v>
       </c>
       <c r="R5" t="n">
-        <v>6564523.305359282</v>
+        <v>6564523</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,19 +1064,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105312229</v>
+        <v>105315441</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599369.2540848248</v>
+        <v>599307</v>
       </c>
       <c r="R6" t="n">
-        <v>6564593.235301045</v>
+        <v>6564516</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1231,19 +1171,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,12 +1208,7 @@
         <v>105315438</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599062.5883968532</v>
+        <v>599063</v>
       </c>
       <c r="R7" t="n">
-        <v>6564544.771306769</v>
+        <v>6564545</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,19 +1273,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,15 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105315442</v>
+        <v>105315439</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,14 +1343,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tåsjön, Srm</t>
+          <t>Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599526.5151090247</v>
+        <v>599072</v>
       </c>
       <c r="R8" t="n">
-        <v>6564663.430261035</v>
+        <v>6564529</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1470,21 +1380,11 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1496,7 +1396,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På västra sidan äldre tall ca 22 cm. Finns fler äldre tallar runt detta träd.</t>
+          <t>Två fruktkroppar på gammal tall norr om kolbotten.</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1519,50 +1419,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105310629</v>
+        <v>105315440</v>
       </c>
       <c r="B9" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tåsjön, Srm</t>
+          <t>Dammkärr, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599065.9919533868</v>
+        <v>599089</v>
       </c>
       <c r="R9" t="n">
-        <v>6564630.927242965</v>
+        <v>6564532</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1592,21 +1487,11 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1618,7 +1503,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Ca 2 dm2.</t>
+          <t>På nordvästra sidan. Gammal tall vid kolbotten.</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1641,50 +1526,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105310630</v>
+        <v>105315442</v>
       </c>
       <c r="B10" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dammkärr, Srm</t>
+          <t>Tåsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599076.7222471966</v>
+        <v>599527</v>
       </c>
       <c r="R10" t="n">
-        <v>6564553.848368808</v>
+        <v>6564663</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1714,21 +1594,11 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1740,7 +1610,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stor blåmossa i barrblandskog.</t>
+          <t>På västra sidan äldre tall ca 22 cm. Finns fler äldre tallar runt detta träd.</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -1763,15 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105315440</v>
+        <v>105312228</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1779,34 +1644,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dammkärr, Srm</t>
+          <t>Tåsjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599089.0911557883</v>
+        <v>599213</v>
       </c>
       <c r="R11" t="n">
-        <v>6564532.140845995</v>
+        <v>6564507</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1836,21 +1701,11 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1859,11 +1714,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>På nordvästra sidan. Gammal tall vid kolbotten.</t>
-        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -1885,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105312228</v>
+        <v>105312229</v>
       </c>
       <c r="B12" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599213.440107509</v>
+        <v>599369</v>
       </c>
       <c r="R12" t="n">
-        <v>6564506.689463436</v>
+        <v>6564593</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1958,19 +1803,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 48952-2023 artfynd.xlsx
+++ b/artfynd/A 48952-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310630</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310631</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315437</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315441</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315439</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315440</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315442</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312228</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,8 +1889,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312229</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>